--- a/XLibur.Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
@@ -700,11 +700,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="3" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.424911" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.567768" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="7.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="4" spans="1:8">

--- a/XLibur.Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
@@ -702,7 +702,7 @@
     <x:col min="1" max="3" width="9.140625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="7.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="7.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.139196" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.139196" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="8.710625" style="0" customWidth="1"/>
   </x:cols>
